--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/98.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/98.xlsx
@@ -426,13 +426,13 @@
         <v>-3.686235591072188</v>
       </c>
       <c r="E2">
-        <v>-7.973553441979253</v>
+        <v>-15.28712047689902</v>
       </c>
       <c r="F2">
-        <v>-0.355455084890984</v>
+        <v>-1.919417711580867</v>
       </c>
       <c r="G2">
-        <v>-5.6702155270837</v>
+        <v>-6.61301219898051</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.605286372104556</v>
       </c>
       <c r="E3">
-        <v>-8.288282385512343</v>
+        <v>-12.72551669887616</v>
       </c>
       <c r="F3">
-        <v>-0.2555324385608909</v>
+        <v>-1.450087107074543</v>
       </c>
       <c r="G3">
-        <v>-6.644662862142913</v>
+        <v>-7.419096774603055</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.418507999843135</v>
       </c>
       <c r="E4">
-        <v>-8.891701547034417</v>
+        <v>-13.04819311429271</v>
       </c>
       <c r="F4">
-        <v>-0.906022852222453</v>
+        <v>-1.503129956978004</v>
       </c>
       <c r="G4">
-        <v>-5.431365566107041</v>
+        <v>-6.158707386746032</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.061076332712026</v>
       </c>
       <c r="E5">
-        <v>-10.23316234537859</v>
+        <v>-13.20486925801009</v>
       </c>
       <c r="F5">
-        <v>-0.3781125900923561</v>
+        <v>-2.074056509968076</v>
       </c>
       <c r="G5">
-        <v>-5.429183553770009</v>
+        <v>-5.505996950476611</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.532329587926456</v>
       </c>
       <c r="E6">
-        <v>-10.10624280436562</v>
+        <v>-16.1547987391387</v>
       </c>
       <c r="F6">
-        <v>-0.9863595796807547</v>
+        <v>-1.884628765765497</v>
       </c>
       <c r="G6">
-        <v>-6.730374931718728</v>
+        <v>-8.419262324245196</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.819784691411287</v>
       </c>
       <c r="E7">
-        <v>-11.71203515901152</v>
+        <v>-15.24491962762154</v>
       </c>
       <c r="F7">
-        <v>-1.017747248940231</v>
+        <v>-1.28903508825486</v>
       </c>
       <c r="G7">
-        <v>-5.990328221201567</v>
+        <v>-6.996616530273632</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.930661000198149</v>
       </c>
       <c r="E8">
-        <v>-11.24462871430982</v>
+        <v>-16.35936349548719</v>
       </c>
       <c r="F8">
-        <v>-0.8263736697084749</v>
+        <v>-1.772705560871047</v>
       </c>
       <c r="G8">
-        <v>-4.516498652124224</v>
+        <v>-7.040227246020211</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.872852895180231</v>
       </c>
       <c r="E9">
-        <v>-13.31654595551325</v>
+        <v>-20.17518702009646</v>
       </c>
       <c r="F9">
-        <v>-1.319149556816234</v>
+        <v>-2.229063931849531</v>
       </c>
       <c r="G9">
-        <v>-4.939136395088501</v>
+        <v>-7.306472125796675</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.665489086478244</v>
       </c>
       <c r="E10">
-        <v>-13.41243186415166</v>
+        <v>-17.85423540778921</v>
       </c>
       <c r="F10">
-        <v>-1.504699713206309</v>
+        <v>-1.639332610448507</v>
       </c>
       <c r="G10">
-        <v>-3.099654057869758</v>
+        <v>-7.017937907966903</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.329158909829108</v>
       </c>
       <c r="E11">
-        <v>-15.09443843634665</v>
+        <v>-17.70537088173507</v>
       </c>
       <c r="F11">
-        <v>-1.014912575687851</v>
+        <v>-2.452048839539519</v>
       </c>
       <c r="G11">
-        <v>-3.041192533345132</v>
+        <v>-7.069797614713927</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.889162588038335</v>
       </c>
       <c r="E12">
-        <v>-14.58152082786787</v>
+        <v>-19.63402531923183</v>
       </c>
       <c r="F12">
-        <v>-2.043942869774106</v>
+        <v>-1.423731769787074</v>
       </c>
       <c r="G12">
-        <v>-2.912594897987375</v>
+        <v>-6.573696602255243</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.36914686590639</v>
       </c>
       <c r="E13">
-        <v>-17.57957893075</v>
+        <v>-23.57449509090223</v>
       </c>
       <c r="F13">
-        <v>-1.313319507035331</v>
+        <v>-2.415949416492919</v>
       </c>
       <c r="G13">
-        <v>-1.93874474525198</v>
+        <v>-5.597894122691979</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.795716904577484</v>
       </c>
       <c r="E14">
-        <v>-19.58545290702556</v>
+        <v>-21.2857318718415</v>
       </c>
       <c r="F14">
-        <v>-0.9100768822917538</v>
+        <v>-1.025196756993607</v>
       </c>
       <c r="G14">
-        <v>-2.34398873272964</v>
+        <v>-5.535833098116641</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.19277349939614</v>
       </c>
       <c r="E15">
-        <v>-18.47482201427437</v>
+        <v>-23.99479634897613</v>
       </c>
       <c r="F15">
-        <v>-0.8138653219262024</v>
+        <v>-1.230370937156002</v>
       </c>
       <c r="G15">
-        <v>-1.869163160862396</v>
+        <v>-5.188886574085635</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.582195221879372</v>
       </c>
       <c r="E16">
-        <v>-19.43419734669536</v>
+        <v>-22.34823867131318</v>
       </c>
       <c r="F16">
-        <v>-0.9342312473899845</v>
+        <v>-1.416385807659048</v>
       </c>
       <c r="G16">
-        <v>-0.6893769806131319</v>
+        <v>-2.6037531999262</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.983292321843944</v>
       </c>
       <c r="E17">
-        <v>-20.55999862737225</v>
+        <v>-21.87295721031215</v>
       </c>
       <c r="F17">
-        <v>-0.7618272816823375</v>
+        <v>-0.5111392829405259</v>
       </c>
       <c r="G17">
-        <v>-0.7369645368897586</v>
+        <v>-4.042257137694561</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.41237454556738</v>
       </c>
       <c r="E18">
-        <v>-22.43110974565355</v>
+        <v>-22.98382811218575</v>
       </c>
       <c r="F18">
-        <v>-0.2017332892186741</v>
+        <v>-0.03721952302269234</v>
       </c>
       <c r="G18">
-        <v>-0.12932495996087</v>
+        <v>-2.84200597857904</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.882354738217949</v>
       </c>
       <c r="E19">
-        <v>-22.48825908763035</v>
+        <v>-27.6162079559621</v>
       </c>
       <c r="F19">
-        <v>-0.1541783733587601</v>
+        <v>-0.620275859891958</v>
       </c>
       <c r="G19">
-        <v>1.085219200267592</v>
+        <v>-3.088937588256612</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.402540074589348</v>
       </c>
       <c r="E20">
-        <v>-24.27792107240969</v>
+        <v>-25.57049699384106</v>
       </c>
       <c r="F20">
-        <v>0.0903888186437659</v>
+        <v>-0.7346336365832353</v>
       </c>
       <c r="G20">
-        <v>1.332495338208905</v>
+        <v>-0.8097190625273263</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.9787614591525601</v>
       </c>
       <c r="E21">
-        <v>-24.37166954131649</v>
+        <v>-27.66872919750307</v>
       </c>
       <c r="F21">
-        <v>0.09063732886460575</v>
+        <v>-0.3469883416669703</v>
       </c>
       <c r="G21">
-        <v>0.02024624360485789</v>
+        <v>-3.136679361946533</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.6132975780808007</v>
       </c>
       <c r="E22">
-        <v>-25.79511383309552</v>
+        <v>-28.31406844291415</v>
       </c>
       <c r="F22">
-        <v>0.5329134539954982</v>
+        <v>-1.179215108196119</v>
       </c>
       <c r="G22">
-        <v>2.182440002416548</v>
+        <v>-0.2622013082321432</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.3043323717545296</v>
       </c>
       <c r="E23">
-        <v>-25.29219056675167</v>
+        <v>-29.80926866958172</v>
       </c>
       <c r="F23">
-        <v>0.2538215653790943</v>
+        <v>-0.1559328555178895</v>
       </c>
       <c r="G23">
-        <v>1.883599467668561</v>
+        <v>-2.282734888657926</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.04997255188849271</v>
       </c>
       <c r="E24">
-        <v>-27.07597006379504</v>
+        <v>-28.60245525314462</v>
       </c>
       <c r="F24">
-        <v>1.049055100434023</v>
+        <v>-0.0560565977623531</v>
       </c>
       <c r="G24">
-        <v>1.521132765661381</v>
+        <v>-0.9809135161697948</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.1558724014316623</v>
       </c>
       <c r="E25">
-        <v>-26.47326640116618</v>
+        <v>-30.75301397396525</v>
       </c>
       <c r="F25">
-        <v>0.8803067200749297</v>
+        <v>1.104452998863642</v>
       </c>
       <c r="G25">
-        <v>1.693957986418894</v>
+        <v>-0.5967973143133992</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.3212797649059284</v>
       </c>
       <c r="E26">
-        <v>-28.89369500199992</v>
+        <v>-31.26273447979461</v>
       </c>
       <c r="F26">
-        <v>0.7635764991420345</v>
+        <v>1.464547622330199</v>
       </c>
       <c r="G26">
-        <v>1.111656002372038</v>
+        <v>-1.265730109972715</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.4553271425654339</v>
       </c>
       <c r="E27">
-        <v>-26.77624395464937</v>
+        <v>-31.19881506917634</v>
       </c>
       <c r="F27">
-        <v>0.9885909069688811</v>
+        <v>0.4373306244886717</v>
       </c>
       <c r="G27">
-        <v>1.022249277320288</v>
+        <v>-0.3046045344448473</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.566942001274614</v>
       </c>
       <c r="E28">
-        <v>-26.62014745560497</v>
+        <v>-31.77454034790451</v>
       </c>
       <c r="F28">
-        <v>0.8945811471599707</v>
+        <v>-0.008087498201039326</v>
       </c>
       <c r="G28">
-        <v>1.047222654609222</v>
+        <v>1.00911782863939</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.6640332754594707</v>
       </c>
       <c r="E29">
-        <v>-27.41206434769632</v>
+        <v>-29.15087156936952</v>
       </c>
       <c r="F29">
-        <v>1.303607433109894</v>
+        <v>0.7431721532762771</v>
       </c>
       <c r="G29">
-        <v>2.774352684411018</v>
+        <v>-0.9931065354846914</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.7523257512702319</v>
       </c>
       <c r="E30">
-        <v>-25.78388774603051</v>
+        <v>-29.95350509520003</v>
       </c>
       <c r="F30">
-        <v>0.6512117744218928</v>
+        <v>0.7644611955282244</v>
       </c>
       <c r="G30">
-        <v>2.298122749716331</v>
+        <v>-1.005214243039042</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.8348797626620518</v>
       </c>
       <c r="E31">
-        <v>-27.63492866750981</v>
+        <v>-28.05906101459421</v>
       </c>
       <c r="F31">
-        <v>1.150096042757895</v>
+        <v>0.9114069458456343</v>
       </c>
       <c r="G31">
-        <v>2.508262022047849</v>
+        <v>-3.396581640448589</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.9118569029748753</v>
       </c>
       <c r="E32">
-        <v>-27.54931786639481</v>
+        <v>-29.47141733776547</v>
       </c>
       <c r="F32">
-        <v>0.6834195274101403</v>
+        <v>0.5810705929572475</v>
       </c>
       <c r="G32">
-        <v>2.524874846803317</v>
+        <v>-0.2315940735256429</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.9807411697028842</v>
       </c>
       <c r="E33">
-        <v>-25.70442208414391</v>
+        <v>-26.5878730213523</v>
       </c>
       <c r="F33">
-        <v>1.277202393778257</v>
+        <v>0.09649885660681505</v>
       </c>
       <c r="G33">
-        <v>3.218918831057064</v>
+        <v>-2.142154232165077</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.036743344109893</v>
       </c>
       <c r="E34">
-        <v>-26.54858398086175</v>
+        <v>-28.60719656543064</v>
       </c>
       <c r="F34">
-        <v>0.4764941785582267</v>
+        <v>-0.1876220505119846</v>
       </c>
       <c r="G34">
-        <v>2.323355343508461</v>
+        <v>-1.869304253389452</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.073883617739077</v>
       </c>
       <c r="E35">
-        <v>-24.60953669551738</v>
+        <v>-28.0985538364151</v>
       </c>
       <c r="F35">
-        <v>0.5760349475156292</v>
+        <v>0.666559765660962</v>
       </c>
       <c r="G35">
-        <v>1.156815454694675</v>
+        <v>-1.698477296561641</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.085664208971255</v>
       </c>
       <c r="E36">
-        <v>-23.00546968946841</v>
+        <v>-25.06669973201373</v>
       </c>
       <c r="F36">
-        <v>0.3253635161218736</v>
+        <v>-0.3400159732376068</v>
       </c>
       <c r="G36">
-        <v>1.782803622583979</v>
+        <v>-2.331418372935408</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.066155179304464</v>
       </c>
       <c r="E37">
-        <v>-24.04613113032708</v>
+        <v>-29.1530407084192</v>
       </c>
       <c r="F37">
-        <v>0.3387167986550017</v>
+        <v>0.7727498397606363</v>
       </c>
       <c r="G37">
-        <v>2.690264819507128</v>
+        <v>-0.8673274694464972</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.010313449613596</v>
       </c>
       <c r="E38">
-        <v>-21.55204689975859</v>
+        <v>-24.93099947989988</v>
       </c>
       <c r="F38">
-        <v>0.09238518408451271</v>
+        <v>-0.8024578744222505</v>
       </c>
       <c r="G38">
-        <v>1.575154797416079</v>
+        <v>-0.4690527965610976</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.9151246885731484</v>
       </c>
       <c r="E39">
-        <v>-22.58106110546954</v>
+        <v>-25.56949167261136</v>
       </c>
       <c r="F39">
-        <v>0.2698322505404032</v>
+        <v>-0.3996236348082536</v>
       </c>
       <c r="G39">
-        <v>1.465453717019164</v>
+        <v>-2.99381169402675</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.7789728685753374</v>
       </c>
       <c r="E40">
-        <v>-20.3660259717277</v>
+        <v>-25.86861549471402</v>
       </c>
       <c r="F40">
-        <v>0.1791343036078853</v>
+        <v>0.3746372943425967</v>
       </c>
       <c r="G40">
-        <v>2.558195651739478</v>
+        <v>-1.577380533688774</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.6019889215057085</v>
       </c>
       <c r="E41">
-        <v>-20.43473650784608</v>
+        <v>-24.62815325216292</v>
       </c>
       <c r="F41">
-        <v>0.2501510694172898</v>
+        <v>-1.021955355346452</v>
       </c>
       <c r="G41">
-        <v>1.379472587275475</v>
+        <v>-2.396061718878028</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.3856065649293613</v>
       </c>
       <c r="E42">
-        <v>-19.43405243552712</v>
+        <v>-22.44476762326068</v>
       </c>
       <c r="F42">
-        <v>0.4295414858001479</v>
+        <v>0.08421748149290958</v>
       </c>
       <c r="G42">
-        <v>1.283608418194738</v>
+        <v>-0.6078615934118469</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.1329234280507754</v>
       </c>
       <c r="E43">
-        <v>-19.26952391788044</v>
+        <v>-23.27514937357319</v>
       </c>
       <c r="F43">
-        <v>0.2013469755139541</v>
+        <v>0.4057400052155097</v>
       </c>
       <c r="G43">
-        <v>0.9912450148050949</v>
+        <v>-3.709751269746671</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.1520132412453445</v>
       </c>
       <c r="E44">
-        <v>-18.05860543975538</v>
+        <v>-19.47620347159051</v>
       </c>
       <c r="F44">
-        <v>0.1908780682773739</v>
+        <v>0.1395830735938201</v>
       </c>
       <c r="G44">
-        <v>1.672721920486168</v>
+        <v>-4.373315986934736</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.4651677389494308</v>
       </c>
       <c r="E45">
-        <v>-16.91160184377458</v>
+        <v>-21.62358773213177</v>
       </c>
       <c r="F45">
-        <v>0.2470380647175692</v>
+        <v>-0.5752979950221532</v>
       </c>
       <c r="G45">
-        <v>1.267563244769053</v>
+        <v>-3.740233818033913</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.8014755569210208</v>
       </c>
       <c r="E46">
-        <v>-16.39960351551935</v>
+        <v>-16.45284478442753</v>
       </c>
       <c r="F46">
-        <v>0.8344847488216722</v>
+        <v>0.7387652386933837</v>
       </c>
       <c r="G46">
-        <v>0.8555271286633425</v>
+        <v>-3.124269782008713</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.155236954663573</v>
       </c>
       <c r="E47">
-        <v>-15.77712400689899</v>
+        <v>-17.33696593578906</v>
       </c>
       <c r="F47">
-        <v>0.1603477592797954</v>
+        <v>0.2929528131199402</v>
       </c>
       <c r="G47">
-        <v>2.466446134494285</v>
+        <v>-3.615806615278209</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.519946654336113</v>
       </c>
       <c r="E48">
-        <v>-14.18363098765792</v>
+        <v>-17.47654709012748</v>
       </c>
       <c r="F48">
-        <v>1.193562137117591</v>
+        <v>-0.4966461668611458</v>
       </c>
       <c r="G48">
-        <v>0.6705712318005628</v>
+        <v>-2.631915924570914</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.888557707128335</v>
       </c>
       <c r="E49">
-        <v>-13.18250312488621</v>
+        <v>-15.06808724609602</v>
       </c>
       <c r="F49">
-        <v>0.1996753300951047</v>
+        <v>-0.2116198541710863</v>
       </c>
       <c r="G49">
-        <v>0.603312752275065</v>
+        <v>-3.777354277535911</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.2534008659858</v>
       </c>
       <c r="E50">
-        <v>-13.32192578263436</v>
+        <v>-15.51548689263183</v>
       </c>
       <c r="F50">
-        <v>0.5697037354560326</v>
+        <v>0.3885364709941695</v>
       </c>
       <c r="G50">
-        <v>0.4593786873484631</v>
+        <v>-5.467623064338905</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.606512153506666</v>
       </c>
       <c r="E51">
-        <v>-11.3341158891754</v>
+        <v>-16.41107866865478</v>
       </c>
       <c r="F51">
-        <v>0.7660715417592666</v>
+        <v>0.4635675052375404</v>
       </c>
       <c r="G51">
-        <v>-0.0683073638414361</v>
+        <v>-3.741798960717768</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.94025286668828</v>
       </c>
       <c r="E52">
-        <v>-11.95343905141241</v>
+        <v>-13.98051081451787</v>
       </c>
       <c r="F52">
-        <v>1.073511819634275</v>
+        <v>-0.4413501576220704</v>
       </c>
       <c r="G52">
-        <v>-0.2615122517046599</v>
+        <v>-3.043732198832142</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.246857582374121</v>
       </c>
       <c r="E53">
-        <v>-9.582742152130907</v>
+        <v>-12.16783965330556</v>
       </c>
       <c r="F53">
-        <v>0.2925278606423041</v>
+        <v>0.1150012709157448</v>
       </c>
       <c r="G53">
-        <v>0.307563128236075</v>
+        <v>-5.742527087810743</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.519634238610851</v>
       </c>
       <c r="E54">
-        <v>-9.148914342196086</v>
+        <v>-13.99821714788787</v>
       </c>
       <c r="F54">
-        <v>0.286322560427933</v>
+        <v>0.03464383427237317</v>
       </c>
       <c r="G54">
-        <v>-0.757383578654183</v>
+        <v>-3.793146796901518</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.754877821641633</v>
       </c>
       <c r="E55">
-        <v>-8.025508624269255</v>
+        <v>-10.46337185003252</v>
       </c>
       <c r="F55">
-        <v>-0.07583304113678849</v>
+        <v>-0.4070615457179904</v>
       </c>
       <c r="G55">
-        <v>-0.7358784525535824</v>
+        <v>-4.376055806936872</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.949895650964285</v>
       </c>
       <c r="E56">
-        <v>-5.659643606753938</v>
+        <v>-12.58407887019459</v>
       </c>
       <c r="F56">
-        <v>0.609291413635821</v>
+        <v>0.3538568696759682</v>
       </c>
       <c r="G56">
-        <v>-1.178026338910317</v>
+        <v>-4.570914430466056</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.103862529909634</v>
       </c>
       <c r="E57">
-        <v>-5.309325385994566</v>
+        <v>-9.704372435502925</v>
       </c>
       <c r="F57">
-        <v>0.2835027977888034</v>
+        <v>-0.4610520479302538</v>
       </c>
       <c r="G57">
-        <v>-1.780652209296374</v>
+        <v>-4.281241628755157</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.217748496314773</v>
       </c>
       <c r="E58">
-        <v>-5.570636450133177</v>
+        <v>-8.49995231757887</v>
       </c>
       <c r="F58">
-        <v>-0.3594329051592272</v>
+        <v>-0.107446026329826</v>
       </c>
       <c r="G58">
-        <v>-0.486859985964204</v>
+        <v>-6.543896548052366</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.293991524311625</v>
       </c>
       <c r="E59">
-        <v>-4.614440106465566</v>
+        <v>-9.050361162367157</v>
       </c>
       <c r="F59">
-        <v>-0.0347683838778086</v>
+        <v>0.3547680738190477</v>
       </c>
       <c r="G59">
-        <v>-1.863381648474654</v>
+        <v>-5.67358534162525</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.336387831240816</v>
       </c>
       <c r="E60">
-        <v>-2.594921838004893</v>
+        <v>-7.893680217431963</v>
       </c>
       <c r="F60">
-        <v>-0.5287777100483357</v>
+        <v>-0.5930043482569927</v>
       </c>
       <c r="G60">
-        <v>-2.639869605631008</v>
+        <v>-3.985288568979481</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.349641478752472</v>
       </c>
       <c r="E61">
-        <v>-4.390398383410083</v>
+        <v>-9.363677222009853</v>
       </c>
       <c r="F61">
-        <v>-1.178080244854284</v>
+        <v>-1.108620809762142</v>
       </c>
       <c r="G61">
-        <v>-1.88207804892037</v>
+        <v>-5.213669640524121</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.339017048697232</v>
       </c>
       <c r="E62">
-        <v>-2.220978568347506</v>
+        <v>-7.27980028095217</v>
       </c>
       <c r="F62">
-        <v>-0.230485921769845</v>
+        <v>-0.2898500433240688</v>
       </c>
       <c r="G62">
-        <v>-1.703668189068682</v>
+        <v>-6.69715256342935</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.309217833696632</v>
       </c>
       <c r="E63">
-        <v>-1.254122196865838</v>
+        <v>-4.527312266557988</v>
       </c>
       <c r="F63">
-        <v>-0.0888980518137423</v>
+        <v>-0.2287090736908401</v>
       </c>
       <c r="G63">
-        <v>-2.255513874600773</v>
+        <v>-6.768670068539008</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.265187271655614</v>
       </c>
       <c r="E64">
-        <v>-0.5274425013289838</v>
+        <v>-8.133603298832346</v>
       </c>
       <c r="F64">
-        <v>-1.226683873846142</v>
+        <v>-0.3085959976494216</v>
       </c>
       <c r="G64">
-        <v>-2.083988017580801</v>
+        <v>-6.263148668983157</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.213311206090732</v>
       </c>
       <c r="E65">
-        <v>-0.3879700303667445</v>
+        <v>-5.728191117808044</v>
       </c>
       <c r="F65">
-        <v>-1.075637704884874</v>
+        <v>-0.9674081902395076</v>
       </c>
       <c r="G65">
-        <v>-2.50518858550204</v>
+        <v>-5.800732677053732</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.158219281835652</v>
       </c>
       <c r="E66">
-        <v>0.5937940775481737</v>
+        <v>-4.460345192932559</v>
       </c>
       <c r="F66">
-        <v>-0.8040359143245834</v>
+        <v>-0.5320688137396582</v>
       </c>
       <c r="G66">
-        <v>-1.818356726235953</v>
+        <v>-3.501075422230665</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.103583052832672</v>
       </c>
       <c r="E67">
-        <v>0.1633762085411292</v>
+        <v>-5.327525323031394</v>
       </c>
       <c r="F67">
-        <v>-1.365287136049958</v>
+        <v>-0.6115763454277575</v>
       </c>
       <c r="G67">
-        <v>-2.609702054613473</v>
+        <v>-5.785668588874322</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.051997909280248</v>
       </c>
       <c r="E68">
-        <v>1.582622604915058</v>
+        <v>-4.029959023243568</v>
       </c>
       <c r="F68">
-        <v>-1.512540210673806</v>
+        <v>-2.518798684857103</v>
       </c>
       <c r="G68">
-        <v>-2.529620561233666</v>
+        <v>-4.8143449767397</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.004697025398305</v>
       </c>
       <c r="E69">
-        <v>0.7671395340877872</v>
+        <v>-2.602502503493733</v>
       </c>
       <c r="F69">
-        <v>-1.509895233556667</v>
+        <v>-1.276682473544314</v>
       </c>
       <c r="G69">
-        <v>-1.664834931912654</v>
+        <v>-5.109743510071829</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.961523259522524</v>
       </c>
       <c r="E70">
-        <v>-0.6779916197139849</v>
+        <v>-5.666377447603343</v>
       </c>
       <c r="F70">
-        <v>-1.618718687629841</v>
+        <v>-1.657798576591714</v>
       </c>
       <c r="G70">
-        <v>-2.107015630484983</v>
+        <v>-3.819337507389005</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.921098980316771</v>
       </c>
       <c r="E71">
-        <v>0.5858647195607428</v>
+        <v>-5.752753560825648</v>
       </c>
       <c r="F71">
-        <v>-2.079372143591841</v>
+        <v>-1.645635658016408</v>
       </c>
       <c r="G71">
-        <v>-0.7731465670257555</v>
+        <v>-6.16852480165189</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.881007525236611</v>
       </c>
       <c r="E72">
-        <v>-0.4139996989628337</v>
+        <v>-3.187046985351838</v>
       </c>
       <c r="F72">
-        <v>-1.563774734536956</v>
+        <v>-2.527248860733061</v>
       </c>
       <c r="G72">
-        <v>-0.6159432421127592</v>
+        <v>-5.972622749666803</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.837689388060741</v>
       </c>
       <c r="E73">
-        <v>-0.9347606244229018</v>
+        <v>-3.790674456678266</v>
       </c>
       <c r="F73">
-        <v>-2.216332753235906</v>
+        <v>-2.136821079710792</v>
       </c>
       <c r="G73">
-        <v>-0.3267101240908263</v>
+        <v>-4.39332159478267</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.787614103714684</v>
       </c>
       <c r="E74">
-        <v>1.163104772844476</v>
+        <v>-5.146798453859278</v>
       </c>
       <c r="F74">
-        <v>-1.805547843289839</v>
+        <v>-2.055293159927265</v>
       </c>
       <c r="G74">
-        <v>0.3926583281587143</v>
+        <v>-4.673196668917067</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.729127555468507</v>
       </c>
       <c r="E75">
-        <v>0.8978901641112536</v>
+        <v>-5.523422580129206</v>
       </c>
       <c r="F75">
-        <v>-2.207388042020476</v>
+        <v>-2.578947270341778</v>
       </c>
       <c r="G75">
-        <v>0.228446313994744</v>
+        <v>-4.728147286373087</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.65918660368982</v>
       </c>
       <c r="E76">
-        <v>-0.5276915673994057</v>
+        <v>-4.729141824605848</v>
       </c>
       <c r="F76">
-        <v>-2.680660846996723</v>
+        <v>-2.652349734271245</v>
       </c>
       <c r="G76">
-        <v>0.2486356702500073</v>
+        <v>-2.366192759022403</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.574576550266547</v>
       </c>
       <c r="E77">
-        <v>-1.242801011846663</v>
+        <v>-4.133402955000782</v>
       </c>
       <c r="F77">
-        <v>-2.619174448156528</v>
+        <v>-2.735957684603202</v>
       </c>
       <c r="G77">
-        <v>0.212243641934206</v>
+        <v>-3.145771626887754</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.472169607871839</v>
       </c>
       <c r="E78">
-        <v>-1.74014066973906</v>
+        <v>-5.129431756039862</v>
       </c>
       <c r="F78">
-        <v>-2.089759042455544</v>
+        <v>-2.163713199075275</v>
       </c>
       <c r="G78">
-        <v>0.7258762211850035</v>
+        <v>-1.21340775098581</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.349130978533905</v>
       </c>
       <c r="E79">
-        <v>-2.91129008912876</v>
+        <v>-7.435045426883125</v>
       </c>
       <c r="F79">
-        <v>-3.005018043971703</v>
+        <v>-2.837522983493046</v>
       </c>
       <c r="G79">
-        <v>1.870490987538579</v>
+        <v>-1.563422217174896</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.203033917154648</v>
       </c>
       <c r="E80">
-        <v>-2.835841183686964</v>
+        <v>-7.171778061973201</v>
       </c>
       <c r="F80">
-        <v>-2.815052689324707</v>
+        <v>-2.798439781061563</v>
       </c>
       <c r="G80">
-        <v>1.601657223951714</v>
+        <v>-3.583092836330545</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.032022511578931</v>
       </c>
       <c r="E81">
-        <v>-4.22925716432114</v>
+        <v>-7.763713013411824</v>
       </c>
       <c r="F81">
-        <v>-3.033909013879142</v>
+        <v>-2.904350695346494</v>
       </c>
       <c r="G81">
-        <v>2.737790032574126</v>
+        <v>-2.428542531094971</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.834661351673231</v>
       </c>
       <c r="E82">
-        <v>-4.040487725311402</v>
+        <v>-7.091832381841789</v>
       </c>
       <c r="F82">
-        <v>-3.820872957151923</v>
+        <v>-3.954589680046624</v>
       </c>
       <c r="G82">
-        <v>1.754299650897082</v>
+        <v>-0.1914942648476691</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.609804297710839</v>
       </c>
       <c r="E83">
-        <v>-4.928938097824265</v>
+        <v>-8.390367775067256</v>
       </c>
       <c r="F83">
-        <v>-2.923927502176854</v>
+        <v>-2.880146628204095</v>
       </c>
       <c r="G83">
-        <v>1.893915628251455</v>
+        <v>-1.509229561899107</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.35703683374019</v>
       </c>
       <c r="E84">
-        <v>-7.184398919032578</v>
+        <v>-10.9079774281056</v>
       </c>
       <c r="F84">
-        <v>-3.247800932588599</v>
+        <v>-3.898172061344158</v>
       </c>
       <c r="G84">
-        <v>3.555788723679015</v>
+        <v>0.7195992443417857</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.077203744939317</v>
       </c>
       <c r="E85">
-        <v>-7.204297033822281</v>
+        <v>-12.18142054685456</v>
       </c>
       <c r="F85">
-        <v>-3.703497438012247</v>
+        <v>-2.993430012373941</v>
       </c>
       <c r="G85">
-        <v>3.142387619404575</v>
+        <v>0.9783301267471204</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.771016046491077</v>
       </c>
       <c r="E86">
-        <v>-8.189099747796346</v>
+        <v>-11.33877116045528</v>
       </c>
       <c r="F86">
-        <v>-3.834166597232049</v>
+        <v>-3.343616533335612</v>
       </c>
       <c r="G86">
-        <v>3.947661733301937</v>
+        <v>0.08058134563992732</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.439772808275259</v>
       </c>
       <c r="E87">
-        <v>-11.04742272822379</v>
+        <v>-14.50031170348832</v>
       </c>
       <c r="F87">
-        <v>-4.019421854826728</v>
+        <v>-4.067389297653236</v>
       </c>
       <c r="G87">
-        <v>2.529153559716833</v>
+        <v>-0.3889220848578981</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.085760878167881</v>
       </c>
       <c r="E88">
-        <v>-9.773870926098642</v>
+        <v>-14.27853874591068</v>
       </c>
       <c r="F88">
-        <v>-4.020791146143555</v>
+        <v>-4.45696965882244</v>
       </c>
       <c r="G88">
-        <v>1.759851477775663</v>
+        <v>-0.7470116373047784</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.7118694818167446</v>
       </c>
       <c r="E89">
-        <v>-12.24378216241419</v>
+        <v>-15.46781564675308</v>
       </c>
       <c r="F89">
-        <v>-4.555420296277759</v>
+        <v>-4.400105550089866</v>
       </c>
       <c r="G89">
-        <v>3.259960350322598</v>
+        <v>-0.5126799184154746</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.3215417608574814</v>
       </c>
       <c r="E90">
-        <v>-14.52216159057533</v>
+        <v>-18.76510172664004</v>
       </c>
       <c r="F90">
-        <v>-5.647940809951582</v>
+        <v>-3.791315979852633</v>
       </c>
       <c r="G90">
-        <v>3.008622060090692</v>
+        <v>0.07417968237745068</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.08117460009574735</v>
       </c>
       <c r="E91">
-        <v>-16.11373906531115</v>
+        <v>-19.33110210743674</v>
       </c>
       <c r="F91">
-        <v>-5.102043378037097</v>
+        <v>-4.397772039116179</v>
       </c>
       <c r="G91">
-        <v>3.232549025414997</v>
+        <v>0.1876147929090139</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.4919801188093282</v>
       </c>
       <c r="E92">
-        <v>-19.25554904709277</v>
+        <v>-21.15692848564133</v>
       </c>
       <c r="F92">
-        <v>-4.890031853331994</v>
+        <v>-5.435249195608781</v>
       </c>
       <c r="G92">
-        <v>2.531601351000179</v>
+        <v>1.509625521652409</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.9066713656904374</v>
       </c>
       <c r="E93">
-        <v>-19.18166699365763</v>
+        <v>-23.74646841981751</v>
       </c>
       <c r="F93">
-        <v>-5.418214648337612</v>
+        <v>-4.861628791824804</v>
       </c>
       <c r="G93">
-        <v>3.519609974764577</v>
+        <v>-1.484259465831733</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.319188930330989</v>
       </c>
       <c r="E94">
-        <v>-20.15367224008601</v>
+        <v>-24.64742190906556</v>
       </c>
       <c r="F94">
-        <v>-6.024034521435808</v>
+        <v>-6.627462897842122</v>
       </c>
       <c r="G94">
-        <v>2.642824918200676</v>
+        <v>-1.099385301795106</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.724757172179426</v>
       </c>
       <c r="E95">
-        <v>-24.22255142071791</v>
+        <v>-26.53708165688227</v>
       </c>
       <c r="F95">
-        <v>-6.332988226555731</v>
+        <v>-6.093919737372988</v>
       </c>
       <c r="G95">
-        <v>2.243086820499764</v>
+        <v>-0.4023980618025376</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.117918712353656</v>
       </c>
       <c r="E96">
-        <v>-25.60235933695903</v>
+        <v>-28.9160611351238</v>
       </c>
       <c r="F96">
-        <v>-5.926030374010598</v>
+        <v>-5.912172615729165</v>
       </c>
       <c r="G96">
-        <v>2.421641054100068</v>
+        <v>-0.988712979816595</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.492471130434666</v>
       </c>
       <c r="E97">
-        <v>-27.11237899481672</v>
+        <v>-29.12044022403798</v>
       </c>
       <c r="F97">
-        <v>-6.188717274581961</v>
+        <v>-6.125014164571874</v>
       </c>
       <c r="G97">
-        <v>1.439404099058732</v>
+        <v>-1.71520496407169</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.842952158025768</v>
       </c>
       <c r="E98">
-        <v>-30.50094778951329</v>
+        <v>-30.83046899339244</v>
       </c>
       <c r="F98">
-        <v>-5.935251759938563</v>
+        <v>-6.406147978836178</v>
       </c>
       <c r="G98">
-        <v>1.435450227079601</v>
+        <v>-1.842611516003369</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>3.162169457805296</v>
       </c>
       <c r="E99">
-        <v>-33.45183957136853</v>
+        <v>-33.75028185813304</v>
       </c>
       <c r="F99">
-        <v>-5.731291138021269</v>
+        <v>-6.80195600613963</v>
       </c>
       <c r="G99">
-        <v>1.451849772433706</v>
+        <v>-0.5224415525548225</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>3.445804165368933</v>
       </c>
       <c r="E100">
-        <v>-35.57506895155287</v>
+        <v>-37.78567523771521</v>
       </c>
       <c r="F100">
-        <v>-6.483638021714759</v>
+        <v>-6.823870051596989</v>
       </c>
       <c r="G100">
-        <v>0.4144095458762733</v>
+        <v>-1.687895357032432</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>3.685330849549895</v>
       </c>
       <c r="E101">
-        <v>-37.89695342950569</v>
+        <v>-39.36894749112097</v>
       </c>
       <c r="F101">
-        <v>-6.483856296525397</v>
+        <v>-7.196712835208928</v>
       </c>
       <c r="G101">
-        <v>1.231870116645414</v>
+        <v>-2.247232071384734</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>3.879619437031692</v>
       </c>
       <c r="E102">
-        <v>-37.90650171695086</v>
+        <v>-40.39785527769273</v>
       </c>
       <c r="F102">
-        <v>-6.125299122958436</v>
+        <v>-5.452678045763682</v>
       </c>
       <c r="G102">
-        <v>-0.3460266754112774</v>
+        <v>-2.211594724027606</v>
       </c>
     </row>
   </sheetData>
